--- a/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,55; 87,61</t>
+          <t>63,88; 87,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,62; 82,14</t>
+          <t>56,58; 81,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,82; 81,34</t>
+          <t>64,92; 82,01</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,23; 84,87</t>
+          <t>69,49; 85,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,78; 86,12</t>
+          <t>72,51; 87,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,15; 84,34</t>
+          <t>74,61; 84,26</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,36; 78,02</t>
+          <t>60,59; 78,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,25; 79,46</t>
+          <t>62,52; 79,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,08; 76,68</t>
+          <t>63,94; 76,45</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,86; 90,54</t>
+          <t>73,61; 90,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,45; 81,08</t>
+          <t>64,61; 81,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,88; 83,75</t>
+          <t>71,92; 84,5</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,94; 83,11</t>
+          <t>72,62; 82,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 78,79</t>
+          <t>69,59; 78,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,56; 79,51</t>
+          <t>72,88; 79,43</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23177</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18421</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41597</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>19129; 26191</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14830; 21273</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36454; 46052</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>58355</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78805</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>137160</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>51822; 63460</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70943; 85395</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>128640; 145278</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>59226</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83954</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143179</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>51086; 66433</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73704; 93590</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>129297; 154583</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>115919</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>107115</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>223034</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>105041; 129077</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>93182; 116913</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206356; 242442</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>256677</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>288294</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>544970</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>240776; 274374</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>268712; 303539</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>523082; 570088</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,88; 87,46</t>
+          <t>62,78; 88,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,58; 81,17</t>
+          <t>57,48; 81,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,92; 82,01</t>
+          <t>64,64; 81,84</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,49; 85,1</t>
+          <t>70,97; 85,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,51; 87,28</t>
+          <t>72,99; 86,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,61; 84,26</t>
+          <t>74,65; 84,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,59; 78,79</t>
+          <t>60,68; 78,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,52; 79,39</t>
+          <t>62,54; 78,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,94; 76,45</t>
+          <t>63,88; 76,11</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,61; 90,45</t>
+          <t>74,06; 90,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,61; 81,07</t>
+          <t>64,73; 80,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,92; 84,5</t>
+          <t>71,75; 84,94</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,62; 82,76</t>
+          <t>73,19; 82,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,59; 78,61</t>
+          <t>69,54; 78,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,88; 79,43</t>
+          <t>72,34; 79,33</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19129; 26191</t>
+          <t>18800; 26422</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14830; 21273</t>
+          <t>15064; 21320</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36454; 46052</t>
+          <t>36296; 45955</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51822; 63460</t>
+          <t>52929; 63537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70943; 85395</t>
+          <t>71422; 84680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128640; 145278</t>
+          <t>128719; 146148</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51086; 66433</t>
+          <t>51165; 65875</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73704; 93590</t>
+          <t>73724; 92579</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129297; 154583</t>
+          <t>129167; 153899</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105041; 129077</t>
+          <t>105683; 128615</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93182; 116913</t>
+          <t>93350; 116188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206356; 242442</t>
+          <t>205871; 243707</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>240776; 274374</t>
+          <t>242664; 275054</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>268712; 303539</t>
+          <t>268513; 303444</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>523082; 570088</t>
+          <t>519201; 569331</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,78; 88,23</t>
+          <t>54,97; 81,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,48; 81,35</t>
+          <t>64,32; 87,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,64; 81,84</t>
+          <t>64,07; 81,32</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,97; 85,2</t>
+          <t>73,39; 86,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,99; 86,55</t>
+          <t>68,28; 83,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,65; 84,76</t>
+          <t>73,81; 83,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,68; 78,13</t>
+          <t>62,34; 79,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,54; 78,54</t>
+          <t>60,81; 77,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,88; 76,11</t>
+          <t>65,02; 76,61</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,06; 90,13</t>
+          <t>64,51; 80,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,73; 80,57</t>
+          <t>70,23; 82,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,75; 84,94</t>
+          <t>69,51; 79,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,19; 82,96</t>
+          <t>69,8; 78,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,54; 78,58</t>
+          <t>70,41; 78,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,34; 79,33</t>
+          <t>71,34; 77,37</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>35323</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18800; 26422</t>
+          <t>11520; 17031</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15064; 21320</t>
+          <t>17421; 23783</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36296; 45955</t>
+          <t>30780; 39067</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>97</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>58355</t>
+          <t>68480</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137160</t>
+          <t>120340</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52929; 63537</t>
+          <t>61933; 73135</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71422; 84680</t>
+          <t>46224; 56619</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128719; 146148</t>
+          <t>112263; 127690</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>80884</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>139411</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51165; 65875</t>
+          <t>70526; 90053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73724; 92579</t>
+          <t>51209; 65202</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129167; 153899</t>
+          <t>128306; 151191</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>115919</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>107115</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>196218</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105683; 128615</t>
+          <t>89979; 112170</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93350; 116188</t>
+          <t>85519; 100912</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205871; 243707</t>
+          <t>181592; 208055</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>351</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>256677</t>
+          <t>266611</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>242664; 275054</t>
+          <t>249873; 282316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>268513; 303444</t>
+          <t>211785; 236506</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>519201; 569331</t>
+          <t>469918; 509658</t>
         </is>
       </c>
     </row>
